--- a/data/trans_dic/IP31KM10_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 55,56</t>
+          <t>52,3; 70,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,19; 69,5</t>
+          <t>40,67; 56,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,46; 60,98</t>
+          <t>49,28; 62,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 61,91</t>
+          <t>59,59; 70,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,18; 68,72</t>
+          <t>51,96; 64,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,31; 64,45</t>
+          <t>58,23; 66,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,77; 73,53</t>
+          <t>41,76; 56,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,26; 56,65</t>
+          <t>39,86; 54,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,52; 63,78</t>
+          <t>42,94; 53,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,73; 55,58</t>
+          <t>46,23; 59,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,46; 60,72</t>
+          <t>42,83; 56,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,22; 55,81</t>
+          <t>46,33; 55,76</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,56; 58,75</t>
+          <t>54,18; 61,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,95; 60,33</t>
+          <t>47,92; 54,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,98; 58,06</t>
+          <t>52,35; 57,17</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>75575</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79997</t>
+          <t>57714</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135030</t>
+          <t>133289</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46233; 63474</t>
+          <t>64280; 86752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64568; 95082</t>
+          <t>48230; 67281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119157; 153098</t>
+          <t>119019; 149722</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>155</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>102915</t>
+          <t>151813</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>105615</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259221</t>
+          <t>257427</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90450; 115223</t>
+          <t>137798; 163993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141537; 170090</t>
+          <t>93844; 116886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239852; 279478</t>
+          <t>239823; 273447</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>103736</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89242</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192979</t>
+          <t>154552</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84288; 138413</t>
+          <t>69545; 94526</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75534; 103724</t>
+          <t>61795; 83766</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169026; 236828</t>
+          <t>138083; 171806</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>80705</t>
+          <t>87793</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94275</t>
+          <t>80684</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174980</t>
+          <t>168476</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70305; 91447</t>
+          <t>76815; 99481</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82385; 107667</t>
+          <t>70235; 92022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157999; 190772</t>
+          <t>152942; 184087</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>459</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>342390</t>
+          <t>396963</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>317176; 383688</t>
+          <t>372106; 422138</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>394361; 449275</t>
+          <t>296244; 339309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>726618; 811629</t>
+          <t>683147; 746073</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM10_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>61,5%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>52,3; 70,59</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40,67; 56,73</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49,28; 62,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>65,65%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>58,48%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>62,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>59,59; 70,92</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51,96; 64,72</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58,23; 66,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>49,11%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46,94%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>41,76; 56,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39,86; 54,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>42,94; 53,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>52,83%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>46,23; 59,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42,83; 56,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46,33; 55,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>57,8%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>54,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>54,18; 61,46</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>47,92; 54,89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52,35; 57,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6149546912972434</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4866350593438292</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5519369390861789</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>75575</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57714</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>133289</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5230464379030337</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4066670380429794</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4928434120542265</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>64280; 86752</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48230; 67281</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>119019; 149722</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7058946347970276</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5673054152220511</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.619980213028303</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6565122055259605</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5848259468655149</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6250771040279933</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>151813</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>105615</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>257427</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5959056840140524</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5196413562617649</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.582329727080134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>137798; 163993</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93844; 116886</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>239823; 273447</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7091885093021508</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6472330244652877</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6639746201675101</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4911222049123485</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4693640483086364</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4806316427646901</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>81783</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>72769</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>154552</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4176297229045279</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3985808160079681</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4294145369327543</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>69545; 94526</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>61795; 83766</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>138083; 171806</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5676511642838696</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.540292545810502</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5342890286942577</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5283463710490547</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4920358957262703</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.510311344261808</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>87793</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>80684</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168476</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4622835415025813</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4283186705948483</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4632599431551699</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>76815; 99481</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70235; 92022</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>152942; 184087</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.598687542417202</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5611790070879977</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5575956801492267</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5779695179639944</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5124201323071548</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.546918054504778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>396963</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>316782</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>713745</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5417774523957127</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4791986775420555</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5234715923038582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>372106; 422138</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>296244; 339309</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>683147; 746073</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.6146233280482842</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5488594877709888</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5716900342889292</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman frutos secos con regularidad (al menos 2-3 veces a la semana) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>75575</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>57714</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>133289</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>64280</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>48230</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>119019</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>86752</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>67281</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>149722</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>151813</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>105615</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>257427</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>137798</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>93844</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>239823</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>163993</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>116886</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>273447</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>81783</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>72769</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>154552</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>69545</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>61795</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>138083</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>94526</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>83766</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>171806</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>87793</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>80684</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>168476</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>76815</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>70235</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>152942</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>99481</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>92022</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>184087</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>519</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>459</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>396963</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>316782</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>713745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>372106</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>296244</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>683147</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>422138</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>339309</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>746073</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>